--- a/Prototype/Textes des premières minutes.xlsx
+++ b/Prototype/Textes des premières minutes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premières minutes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Premières minutes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,13 +891,13 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[3] ponts coupés : elles restent sur leur rive. Cliquez sur un lieu pour les abriter.</t>
+          <t>Trouvez un champ où poser des containers pour les loger.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Ne désigne aucun champ.</t>
+          <t>Ne désigne aucun champ. Les ponts coupés ne sont plus dits ici (2026-10-06).</t>
         </is>
       </c>
     </row>
@@ -914,13 +914,13 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Un camp demande un terrain nu.</t>
+          <t>(retiré le 2026-10-06)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Ne s'affiche qu'après 3 lieux ouverts sans avoir ouvert de champ.</t>
+          <t>Inutile depuis que le guide dit « un champ ».</t>
         </is>
       </c>
     </row>
@@ -1070,11 +1070,15 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Jusqu'à [238] personnes · [119] containers</t>
+          <t>(retiré le 2026-10-06)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Prix, abrités et nourris sont dans les conséquences du bas.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1089,11 +1093,15 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>⚠ Il ne sera plus jamais cultivé.</t>
+          <t>(retiré le 2026-10-06)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1884,13 +1892,13 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>La boue bloque le chemin jusqu'au pont : déblayez-le pendant le chantier.</t>
+          <t>La boue bloque le chemin jusqu'au pont. Revenez sur la ville pour la voir, et déblayez pendant le chantier.</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr"/>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Ne nomme pas la rue : le joueur la cherche.</t>
+          <t>Ne nomme pas la rue. La tuile Ville s'entoure en jaune tant qu'on n'y est pas revenu.</t>
         </is>
       </c>
     </row>
@@ -2021,11 +2029,15 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Encore [12] rues sous la boue : Trafic propose de tout déblayer d'un coup.</t>
+          <t>Encore [12] rues sous la boue : ouvrez Trafic pour tout déblayer d'un coup.</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>La tuile Trafic s'entoure en jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -3165,7 +3177,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Un premier lieu à relever</t>
+          <t>Un premier lieu à relever   /   rue déjà déblayée : Reconstruisons quelque chose pour les habitants</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
@@ -3185,6 +3197,8 @@
       <c r="C143" s="4" t="inlineStr">
         <is>
           <t>Rue des Forgerons envasée, [43] logements inhabitables à côté. La prochaine crue y mettrait [5,1] m d'eau. Par où commencer ?
+[6] autres îlots attendent. La caisse ne les relèvera pas tous.
+— rue déjà déblayée : [Maisons des Forgerons] : [43] logements inhabitables. La prochaine crue y mettrait [5,1] m d'eau.
 [6] autres îlots attendent. La caisse ne les relèvera pas tous.</t>
         </is>
       </c>
@@ -3204,7 +3218,8 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>① Déblayer la rue   ·   ② Relever les logements · [43] personnes peuvent rentrer</t>
+          <t>① Déblayer la rue   ·   ② Relever les logements · [43] personnes peuvent rentrer
+— rue déjà déblayée : Relever [Maisons des Forgerons] · [43] personnes peuvent rentrer</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>

--- a/Prototype/Textes des premières minutes.xlsx
+++ b/Prototype/Textes des premières minutes.xlsx
@@ -1051,11 +1051,15 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Relogement</t>
+          <t>(retiré le 2026-10-06)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Le bouton « Installer… » suffit.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -3177,11 +3181,15 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Un premier lieu à relever   /   rue déjà déblayée : Reconstruisons quelque chose pour les habitants</t>
+          <t>Le pont est rouvert</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Ne désigne aucun îlot : le joueur choisit (2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="49" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
@@ -3196,10 +3204,8 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Rue des Forgerons envasée, [43] logements inhabitables à côté. La prochaine crue y mettrait [5,1] m d'eau. Par où commencer ?
-[6] autres îlots attendent. La caisse ne les relèvera pas tous.
-— rue déjà déblayée : [Maisons des Forgerons] : [43] logements inhabitables. La prochaine crue y mettrait [5,1] m d'eau.
-[6] autres îlots attendent. La caisse ne les relèvera pas tous.</t>
+          <t>[238] personnes vivent encore dans les containers. Choisissez un îlot à reconstruire.
+[7] îlots attendent. La caisse ne les relèvera pas tous.</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr"/>
@@ -3218,12 +3224,15 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>① Déblayer la rue   ·   ② Relever les logements · [43] personnes peuvent rentrer
-— rue déjà déblayée : Relever [Maisons des Forgerons] · [43] personnes peuvent rentrer</t>
+          <t>(retiré le 2026-10-06)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
-      <c r="E144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Plus de bouton : on clique sur l'îlot dans la ville.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="94" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -3238,7 +3247,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>[8] bâtiments détruits, [43] logements perdus. La crue annoncée en reprendrait [100] %.
+          <t>[8] bâtiments détruits, [43] logements perdus. Relevé, [43] personnes quittent le camp. La crue annoncée en reprendrait [100] %.
 Comment le relever ?
 — bouton : Comme avant
 Autrement qu'avant : un concours, pour tous les îlots sinistrés.
@@ -3246,7 +3255,11 @@
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Le nombre qui quitte le camp sert à comparer les îlots.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="19" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
@@ -3300,7 +3313,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Laisser avancer · ×12   ·   Voir mon chantier   ·   Comparer les logements / Comparer la rue</t>
+          <t>Laisser avancer · ×12   ·   Voir mon chantier</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>

--- a/Prototype/Textes des premières minutes.xlsx
+++ b/Prototype/Textes des premières minutes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="36000" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premières minutes" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,11 +54,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -116,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -133,21 +137,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,1724 +528,1770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F99"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="7" min="1" max="1"/>
-    <col width="30" customWidth="1" style="7" min="2" max="2"/>
-    <col width="70" customWidth="1" style="7" min="3" max="3"/>
-    <col width="50" customWidth="1" style="7" min="4" max="4"/>
-    <col width="18" customWidth="1" style="7" min="5" max="5"/>
-    <col width="40" customWidth="1" style="7" min="6" max="6"/>
+    <col width="8.6640625" customWidth="1" style="10" min="1" max="1"/>
+    <col width="30" customWidth="1" style="10" min="2" max="2"/>
+    <col width="70" customWidth="1" style="10" min="3" max="3"/>
+    <col width="50" customWidth="1" style="10" min="4" max="4"/>
+    <col width="18" customWidth="1" style="10" min="5" max="5"/>
+    <col width="40" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" s="7">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="48" customHeight="1" s="10">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Textes des premières minutes, d'après le jeu du 2026-10-20. Entre [crochets] : ce que le jeu calcule (exemple d'une partie). Garde le crochet là où tu veux le chiffre, efface-le sinon. Laisse « Ta version » vide pour garder le texte, écris « enlève » pour le retirer. Les textes marqués « Claude — flaggable » sont à réécrire pour la déclaration Steam (décision 90).</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="16" customHeight="1" s="10">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Où à l'écran</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Texte actuel</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Ta version</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Qui l'a écrit</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>À garder en tête</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>0 · Avant de jouer : le choix du mode</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="10">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Écran d'accueil · titre</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Wehrau, après la crue</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="10">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Écran d'accueil · boutons</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Mode histoire   ·   Mode auteur</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>« Mode auteur » : outil d'essai.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1 · Le récit : cinq pages, en bas de l'écran, le temps arrêté</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7" ht="48" customHeight="1" s="10">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Page 1 · titre + texte</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Wehrau
 Petite ville du Grobwald nichée à la sortie d'une vallée, Wehrau subit souvent des crues. Mais celle-ci est inhabituelle.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Ta version du 2026-10-07, déjà dans le jeu.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8" ht="48" customHeight="1" s="10">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Page 2 · titre + texte</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>La crue
-L'Ilse est sortie de son lit et a dévasté une partie de la ville. Les trois ponts reliant le faubourg au centre-ville ont été arrachés par le courant.</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
+L'Ilse est sortie de son lit et a dévasté une partie de la ville. Les trois ponts reliant le faubourg au centre-ville ont été arrachés par le courant. [260] personnes ont perdu leur logement du jour au lendemain et il n'y a plus aucun moyen de traverser l'Ilse.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Ta version, déjà dans le jeu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Pages 2 et 3 fusionnées le 2026-10-20, avec tes mots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="10">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Page 3 · titre + texte</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Les dégâts
-[260] personnes ont perdu leur logement du jour au lendemain et il n'y a plus aucun moyen de traverser l'Ilse.</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>(fusionnée dans la page 2)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Ta version, déjà dans le jeu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" s="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Page 4 · titre</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Page 3 · titre</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Le budget</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Ajoutée le 2026-10-18.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11" ht="80" customHeight="1" s="10">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Page 4 · texte</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Un budget d'urgence de [1,5 million] d'euros vous a été attribué : abriter les sinistrés, rouvrir un pont, déblayer les rues. Quand les deux rives seront reconnectées, la mairie pourra débloquer un budget de reconstruction. Un nouveau budget sera voté chaque janvier. L'Ilse reviendra : ce qui sera rebâti au bord de l'eau, elle pourra le reprendre.</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>D'après ta consigne du 2026-10-20.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Page 3 · texte</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Un budget d'urgence de [1,5 million] d'euros vous a été attribué. Abritez les sinistrés et reconstruisez au moins un pont. Quand les deux rives seront reconnectées, la mairie pourra débloquer un budget supplémentaire pour la reconstruction des logements détruits.</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" s="10">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1.5b</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Page 4 · texte, sans titre</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Une crue reviendra, mais personne ne sait quand. Certains disent qu'elle sera encore plus destructrice que celle-là.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" s="10">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Page 5 · titre + texte</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Que faire ?
 Trouvez un champ libre pour accueillir temporairement les sinistrés.</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Ta version, déjà dans le jeu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2 · Abriter les sinistrés</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
+          <t>2 · Abriter les sinistrés</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" s="10">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>[3] ponts coupés : les sinistrés restent sur leur rive. Cliquez sur un champ de cette rive pour y poser un camp.</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>D'après ta version du 2026-10-07.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16" ht="32" customHeight="1" s="10">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Guide · un camp posé, pas assez</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Il manque encore [22] places : cliquez sur un autre champ.</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Il manque encore [22] places : trouvez un autre champ disponible.</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1" s="10">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Guide · camp sur l'autre rive</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>[Champ des Luzernes] est sur l'autre rive.</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Ajouté sous le texte du guide.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="18" ht="16" customHeight="1" s="10">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un champ · bouton</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Installer [119] containers</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1" s="10">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un champ de l'autre rive</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>⚠ Autre rive : inaccessible</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Ta version (orthographe corrigée).</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="20" ht="16" customHeight="1" s="10">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Fiche du camp vide</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Camp vide : aucun pont n'y mène.</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="10">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un champ, tout le monde casé · bouton grisé</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Rien à reloger</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1" s="10">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Compteurs en bas à droite</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>−[104] k€ par mois d'aide d'urgence   ·   [260] personnes sans logement   ·   [238] places en construction</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" s="10">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>[119] containers livrés, [238] personnes accueillies.</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1" s="10">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>[238] personnes abritées, [22] encore dehors.  
   [22] personnes abritées, plus personne dehors.</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="16" customHeight="1" s="10">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Bulle de confiance</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>[Champ des Luzernes] : un toit pour la nuit   ·   plus personne ne dort dehors</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>3 · Choisir un pont</t>
-        </is>
-      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>3 · Choisir un pont</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="10">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>[3] ponts sont coupés : les deux rives ne se rejoignent plus. Cliquez sur Chantiers, dans la colonne de gauche, puis sur un pont coupé.</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>La tuile Chantiers s'entoure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>[3] ponts sont coupés : les deux rives sont séparées. Cliquez sur Chantiers, dans la colonne de gauche, puis sur les ponts coupés pour comparer le coût et la durée d'une construction.</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="10">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Cliquez sur un pont coupé, dans Chantiers ou sur la carte, puis choisissez comment le rebâtir dans sa fiche.
-Les ponts ne coûtent pas tous le même prix, ni le même temps.</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Ne dit pas lequel choisir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Cliquez sur un pont coupé, dans Chantiers ou sur la carte, puis choisissez comment le rebâtir dans sa fiche.</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Ton choix du 2026-10-20 : la 2ᵉ phrase est partie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1" s="10">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Panneau Chantiers · légende</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Cassé, rien d'engagé   ·   Chantier en cours   ·   Fait, la ville est réparée là</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Détruit / Endommagé   ·   Chantier en cours   ·   Chantier terminé</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="10">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Panneau Chantiers · titre de la liste</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Ponts coupés</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Suivi d'un bouton par pont, son nom seul.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31" ht="16" customHeight="1" s="10">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont · texte</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Le tablier est parti ; la rive droite n'a plus d'accès routier.</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>ndl: je comprends pas ce texte</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Veut dire : plus de route vers l'autre rive. Les rues de la rive droite existent toujours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1" s="10">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont · boutons</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Rebâtir en dur   ·   Pont provisoire</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Aucun des deux n'est conseillé.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="16" customHeight="1" s="10">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont · avant le fonds</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Le pont en dur attend le fonds de reconstruction, demandé à la mairie.</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1" s="10">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont · état</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>franchissement emporté   ·   en chantier, boue sur le chemin   ·   en chantier, chemin dégagé   ·   pont livré, accès coupé   ·   liaison provisoire   ·   liaison ouverte</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="10">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont en chantier</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Pont provisoire en cours  
   Chantier en cours</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1" s="10">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont provisoire</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Provisoire : une voie, en alternat.
 Le fonds de reconstruction, demandé à la mairie, paiera un pont en dur.   — bouton : Remplacer par un pont en dur</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Après le fonds : « Le pont en dur se bâtit à côté ; le provisoire reste ouvert. »</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>4 · La boue</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
+          <t>4 · La boue</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1" s="10">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>La boue bloque le chemin jusqu'au pont.
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>La boue bloque encore le chemin jusqu'au pont.
 Cliquez sur les rues boueuses pour les déblayer.</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>La tuile Ville s'entoure en même temps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="10">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Panneau Chantiers</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Cliquez sur Ville, en haut de la colonne de gauche, pour voir ce qui barre le chemin du pont.</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1" s="10">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Fiche d'une rue boueuse</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>La rue a gardé [3,8] m de limon.   — bouton : Déblayer la rue</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>— bouton : Déblayer la rue</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>La phrase sur le limon est partie (2026-10-20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1" s="10">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut (3ᵉ rue déblayée)</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Encore [16] rues sous la boue.
 Cliquez sur Chantiers pour tout déblayer.</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>Corrigé le 2026-10-20 : disait encore « Trafic ».</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42" ht="32" customHeight="1" s="10">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Panneau Chantiers</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>[19] rues sous la boue   — bouton : Tout déblayer, [1,3 mois], [155] k€</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>Le bouton a la même forme que « Mettre en place ».</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="43" ht="48" customHeight="1" s="10">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Déblaiement de [19] rues : −[155] k€, [1,3 mois]  
   Rue déblayée.  
   Toutes les rues sont déblayées.</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1" s="10">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Chemin du pont dégagé.</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1" s="10">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>Guide (pont fini, chemin bloqué)</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>La boue bloque encore le chemin jusqu'au pont : cliquez sur une rue boueuse pour la déblayer.</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>Autre cas : « Aucun accès continu : une rue voisine est fermée. »</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46" ht="32" customHeight="1" s="10">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Pont provisoire posé.  
   Pont rebâti.   (+ « Ses accès restent coupés. » si la boue bloque)</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>5 · La reconstruction, pendant le pont</t>
-        </is>
-      </c>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
+          <t>5 · La reconstruction, pendant le pont</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1" s="10">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>Guide · titre</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>Nouveau le 2026-10-20.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="49" ht="48" customHeight="1" s="10">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>Avant de rebâtir, déblayez toutes les rues : [12] sont encore sous la boue. Cliquez sur une rue boueuse pour la déblayer.
 Ou cliquez sur Chantiers, dans la colonne de gauche, puis sur « Tout déblayer ».</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>La 2ᵉ phrase n'apparaît qu'après 3 rues à la main.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="50" ht="32" customHeight="1" s="10">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Commencez par les Maisons du Lavoir, qui clignotent : leurs maisons tiennent debout, il suffit de les nettoyer. C'est le chantier le plus court.</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Ensuite : « Cliquez sur un îlot qui clignote pour le rebâtir. »</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Commencez par les Maisons du Lavoir : leurs maisons tiennent debout, il suffit de les nettoyer. C'est le chantier le plus court.</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" s="10">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Guide · rues engagées, campement amélioré</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Quand le pont rouvrira, la mairie pourra débloquer un nouveau budget. D'ici là, cliquez sur ×4 pour accélérer le temps.</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Nouveau le 2026-10-20. Seul endroit qui parle du ×4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Quand le pont rouvrira, la mairie pourra débloquer un nouveau budget. Vous pouvez cliquer sur ×2 ou ×4 pour accélérer le temps.</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1" s="10">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un îlot sinistré · bouton</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Nettoyer et remettre en état  
   Reconstruire l'îlot</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>« Nettoyer » là où les maisons tiennent debout.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="53" ht="16" customHeight="1" s="10">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un îlot · la première année</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>Rien à engager ici cette année : on rebâtit d'abord.</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="64" customHeight="1" s="10">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un îlot · les quatre façons</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Comme avant : Les maisons d'avant, au même endroit. · Moderne : Plus de logements, isolés, sous un toit plat. · Sur pilotis : Le rez sur poteaux : l'eau passe dessous. · Parc inondable : Personne ne revient : une prairie qui boit la crue.</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Comme avant : garde la forme historique des bâtiments. · Moderne : plus de logements, isolés, sous un toit plat. · Sur pilotis : logements protégés d'une crue. · Parc inondable : protection en cas de crue, mais sans logements.</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Toi, sauf « Moderne » (Claude — flaggable)</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1" s="10">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>[43] logements réhabilités.</t>
         </is>
       </c>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>6 · Le camp se plaint</t>
-        </is>
-      </c>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
+          <t>6 · Le camp se plaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1" s="10">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Carte au centre</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>Les habitants du camp sont mécontents
-Ils ont un toit, pas de quoi vivre.   — boutons : Voir le campement · Plus tard</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>Le temps s'arrête.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+Ils ont un toit, pas de quoi vivre. Une amélioration du campement leur donnerait accès à des sanitaires et à une cantine commune.   — boutons : Voir le campement · Plus tard</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>Toi</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Ta version, dans le jeu depuis le 2026-10-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1" s="10">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>Fiche du camp · bouton</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>Améliorer le campement  
   Améliorer le campement, en cours  
   Campement amélioré</t>
         </is>
       </c>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="16" customHeight="1" s="10">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>[Champ des Luzernes] : le camp n'use plus la confiance.</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="32" customHeight="1" s="10">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>Compteurs en bas à droite</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>[238] personnes vivent dans les containers   ·   Les habitants du camp se plaignent   ·   −[2,6] confiance par mois   ·   « Améliorer le campement » l'arrête</t>
         </is>
       </c>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>7 · Le pont rouvert : la mairie</t>
-        </is>
-      </c>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
+          <t>7 · Le pont rouvert : la mairie</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1" s="10">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>Fiche du pont · journal</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Les deux rives sont reliées.  
   [Pont d'Aval] : les deux rives sont reliées.</t>
         </is>
       </c>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="32" customHeight="1" s="10">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>La mairie a rouvert : elle peut demander le fonds de reconstruction. Cliquez sur la mairie, dans la colonne de gauche.</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="32" customHeight="1" s="10">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>Guide (fonds pas encore demandé)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>Le budget d'urgence ne rebâtira pas tout : demandez le fonds de reconstruction à la mairie.</t>
         </is>
       </c>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>Une fois reçu : « Le prochain budget arrivera en janvier. »</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+    <row r="65" ht="32" customHeight="1" s="10">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>Colonne de gauche · infobulles</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>la mairie : Décide pour la ville.   ·   l'université : Publie les études.   ·   Institut de recherche : Met au point de nouvelles façons de bâtir.   ·   la bibliothèque : Range les concepts.</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n"/>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="16" customHeight="1" s="10">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>Mairie · colonnes</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Budgets   ·   Programmes   ·   Études   ·   Subventions   ·   Règles</t>
         </is>
       </c>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Une colonne vide se retire.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="67" ht="32" customHeight="1" s="10">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>Mairie · Budgets</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>Fonds de reconstruction
 Le pont rouvert, demander à l'État de quoi rebâtir le faubourg. Il ne suffira pas à tout.</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="32" customHeight="1" s="10">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>Journal + bandeau</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>Fonds de reconstruction reçu : +[2 000] k€.  
   Le fonds de reconstruction est arrivé : un pont en dur devient possible.</t>
         </is>
       </c>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="16" customHeight="1" s="10">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut (janvier)</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>Budget de l'an [2] : [360] k€.</t>
         </is>
       </c>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="48" customHeight="1" s="10">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>Mairie · Programmes</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Concours d'urbanisme
 Là où des maisons sont tombées, demander à des architectes d'autres projets que les maisons d'avant.</t>
         </is>
       </c>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Coûte 1 point.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="71" ht="32" customHeight="1" s="10">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>7.10</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>[Concours d'urbanisme] adopté, −1 point.
 Un îlot aux maisons tombées peut lancer un concours.</t>
         </is>
       </c>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="32" customHeight="1" s="10">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>7.11</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>Mairie · Études</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>Étude de la prochaine crue
 Demander à l'université où l'eau reviendra, et comment s'y préparer.</t>
         </is>
       </c>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="80" customHeight="1" s="10">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>7.12</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>Mairie · Études</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>Étude énergétique
 Mesurer ce que la ville consomme, et ce que ses toits pourraient produire.   ·   Étude de circulation
@@ -2240,109 +2299,109 @@
 Savoir ce que portent les champs, et combien d'habitants ils nourrissent.</t>
         </is>
       </c>
-      <c r="D72" s="9" t="n"/>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="48" customHeight="1" s="10">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>7.13</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>Bandeau + journal</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>La mairie peut commander une étude à l'université.  
   Étude commandée à l'université : [80] k€, rendue dans [1 mois].  
   [Étude énergétique] rendue : la carte [Énergie] s'ouvre.</t>
         </is>
       </c>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="16" customHeight="1" s="10">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>7.14</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>Boutons grisés · infobulles</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>Caisse insuffisante   ·   Points insuffisants   ·   Confiance insuffisante</t>
         </is>
       </c>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>8 · Le concours d'architectes</t>
-        </is>
-      </c>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
+          <t>8 · Le concours d'architectes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="96" customHeight="1" s="10">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>Carte au centre · titre + texte</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>Un concours d'architectes
 Des maisons sont tombées. Les reconstruire comme avant, c'est les exposer de nouveau à la crue.
 Un concours demande à des architectes d'autres projets pour toute la zone sinistrée. Il dure [1 mois] et coûte [120] k€. En attendant, on peut toujours reconstruire comme avant.   — bouton : Revenir à l'îlot</t>
         </is>
       </c>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="64" customHeight="1" s="10">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>Fiche d'un îlot · boutons</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>Lancer un concours d'architectes  
   Concours en cours  
@@ -2350,161 +2409,161 @@
   Projet : [moderne], revoir</t>
         </is>
       </c>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="48" customHeight="1" s="10">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>Fenêtre des projets</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>Projets : [Maisons des Forgerons]  
   Lauréats du concours : [Maisons des Forgerons]
 [43] logements perdus. La prochaine crue y mettrait [5,1] m d'eau.</t>
         </is>
       </c>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="16" customHeight="1" s="10">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>Le concours est rendu : moderne, pilotis et parc coûtent [20] % de moins.</t>
         </is>
       </c>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>9 · L'université</t>
-        </is>
-      </c>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
+          <t>9 · L'université</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1" s="10">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>Carte au centre</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Une nouvelle étude a été publiée
 Sur la prochaine crue de l'Ilse.   — bouton : Trouver l'université</t>
         </is>
       </c>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>Tes mots du 2026-10-09.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="83" ht="80" customHeight="1" s="10">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>Guide · titre + texte</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>L'université
 Elle a trois lieux. L'université publie ses études sur Wehrau, la bibliothèque raconte comment d'autres villes s'y sont prises, l'institut met au point de nouvelles façons de bâtir. Chaque objectif atteint, en bas à gauche, rapporte un point à dépenser à la mairie ou à l'institut.</t>
         </is>
       </c>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="16" customHeight="1" s="10">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>Université : une étude annonce une crue plus forte d'ici 6 à 8 ans.</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="96" customHeight="1" s="10">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>Université · études</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>Aucune étude publiée.  
   Nouvelle étude : la prochaine crue · Où l'eau montera
@@ -2513,332 +2572,332 @@
 Les recherches de l'institut, dont les pilotis. — Voir à l'institut</t>
         </is>
       </c>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>10 · Les objectifs, en bas à gauche</t>
-        </is>
-      </c>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
+          <t>10 · Les objectifs, en bas à gauche</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="64" customHeight="1" s="10">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>Liste</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>Abriter tout le monde · Rouvrir un pont · Rebâtir un premier îlot · Rebâtir les logements · Densifier un îlot · Rendre une berge à l'Ilse · Laisser un pré déborder · Rendre un parking perméable · Verdir un toit plat · Poser des panneaux solaires · Retirer des places · Fermer une rue aux voitures · Planter des arbres · Bâtir un pont résistant</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="16" customHeight="1" s="10">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>Bandeau du haut</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>Objectif atteint : [Rouvrir un pont]. Un point de recherche.</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>11 · Après le premier îlot</t>
-        </is>
-      </c>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
+          <t>11 · Après le premier îlot</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1" s="10">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>Guide · titre + texte</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Le premier chantier avance
 [Rue des Forgerons] : chantier en cours.</t>
         </is>
       </c>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="48" customHeight="1" s="10">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>Guide · titre + texte</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>Un lieu reprend vie
 [Maisons des Forgerons] : [43] logements remis en état.
 Cliquez sur l'îlot qui clignote pour voir le résultat.   — bouton : Et maintenant ?</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>Variantes : « rebâti en moderne, [x] logements » · « [x] logements sur pilotis » · « rendu à l'eau » · « [rue] est praticable ».</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+    <row r="92" ht="64" customHeight="1" s="10">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>Guide · titre + texte</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>Réparer ou investir ?
 Pour réparer, cliquez sur un îlot qui clignote.
 Pour investir, cliquez sur Énergie, dans la colonne de gauche : elle montre où le solaire s'amortit.   — bouton : Continuer à mon rythme</t>
         </is>
       </c>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>Ou : « Pour agir autrement, cliquez sur l'institut, dans la colonne de gauche. »</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+    <row r="93" ht="16" customHeight="1" s="10">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>Guide · titre</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>À vous de choisir la suite   — bouton : Revoir les pistes</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="n"/>
+    </row>
+    <row r="94" ht="32" customHeight="1" s="10">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>Infobulles</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Revoir les premiers pas après la crue.   ·   Réduire les premiers pas. Le bouton Début les rouvre.</t>
         </is>
       </c>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>12 · Les noms</t>
-        </is>
-      </c>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
+          <t>12 · Les noms</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1" s="10">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>Ponts</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>Pont d'Aval · Pont du Centre · Pont d'Amont</t>
         </is>
       </c>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>Tous les noms sont dans Godot/data/lieux.json ; 91 lieux n'en ont pas.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+    <row r="97" ht="16" customHeight="1" s="10">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>12.2</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>Îlots et rues du début</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>Maisons du Lavoir · Maisons des Forgerons · Rue des Forgerons</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n"/>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="n"/>
+    </row>
+    <row r="98" ht="16" customHeight="1" s="10">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>Champs atteignables</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>Champ des Luzernes · Champ des Bleuets · Champ de l'Orge</t>
         </is>
       </c>
-      <c r="D97" s="9" t="n"/>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>Claude — flaggable</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Claude — flaggable</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="n"/>
+    </row>
+    <row r="99" ht="16" customHeight="1" s="10">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>Fixes</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>Wehrau · l'Ilse · le Grobwald</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n"/>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="11" t="inlineStr">
         <is>
           <t>Toi</t>
         </is>
       </c>
-      <c r="F98" s="9" t="n"/>
+      <c r="F99" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2853,20 +2912,20 @@
   <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="7" min="1" max="1"/>
-    <col width="30" customWidth="1" style="7" min="2" max="2"/>
-    <col width="70" customWidth="1" style="7" min="3" max="4"/>
-    <col width="34" customWidth="1" style="7" min="5" max="5"/>
+    <col width="8.6640625" customWidth="1" style="10" min="1" max="1"/>
+    <col width="30" customWidth="1" style="10" min="2" max="2"/>
+    <col width="70" customWidth="1" style="10" min="3" max="4"/>
+    <col width="34" customWidth="1" style="10" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="34" customHeight="1" s="10">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Textes des premières minutes — entre [crochets] : ce que le jeu calcule (exemple d'une partie). Garde le crochet là où tu veux le chiffre, efface-le sinon. Laisse « Ta version » vide pour garder le texte actuel.</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" s="10">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>N°</t>
@@ -2893,14 +2952,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" s="7">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3" ht="22" customHeight="1" s="10">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>0 · Avant de jouer : le choix du mode</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1" s="7">
+    <row r="4" ht="19" customHeight="1" s="10">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>0.1</t>
@@ -2919,7 +2978,7 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="5" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1" s="7">
+    <row r="5" ht="34" customHeight="1" s="10">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>0.2</t>
@@ -2942,7 +3001,7 @@
       </c>
       <c r="E5" s="5" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="7">
+    <row r="6" ht="19" customHeight="1" s="10">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>0.3</t>
@@ -2961,7 +3020,7 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="5" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="7">
+    <row r="7" ht="19" customHeight="1" s="10">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>0.4</t>
@@ -2984,7 +3043,7 @@
       </c>
       <c r="E7" s="5" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="7">
+    <row r="8" ht="19" customHeight="1" s="10">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -3007,7 +3066,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="7">
+    <row r="9" ht="34" customHeight="1" s="10">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>0.6</t>
@@ -3034,14 +3093,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1" s="7">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="22" customHeight="1" s="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>1 · Le récit : quatre pages, en bas de l'écran, le temps arrêté</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1" s="7">
+    <row r="11" ht="19" customHeight="1" s="10">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -3064,7 +3123,7 @@
       </c>
       <c r="E11" s="5" t="n"/>
     </row>
-    <row r="12" ht="64" customHeight="1" s="7">
+    <row r="12" ht="64" customHeight="1" s="10">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -3092,7 +3151,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1" s="7">
+    <row r="13" ht="19" customHeight="1" s="10">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
@@ -3115,7 +3174,7 @@
       </c>
       <c r="E13" s="5" t="n"/>
     </row>
-    <row r="14" ht="64" customHeight="1" s="7">
+    <row r="14" ht="64" customHeight="1" s="10">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
@@ -3143,7 +3202,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1" s="7">
+    <row r="15" ht="19" customHeight="1" s="10">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
@@ -3166,7 +3225,7 @@
       </c>
       <c r="E15" s="5" t="n"/>
     </row>
-    <row r="16" ht="34" customHeight="1" s="7">
+    <row r="16" ht="34" customHeight="1" s="10">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>1.6</t>
@@ -3193,7 +3252,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1" s="7">
+    <row r="17" ht="19" customHeight="1" s="10">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -3216,7 +3275,7 @@
       </c>
       <c r="E17" s="5" t="n"/>
     </row>
-    <row r="18" ht="79" customHeight="1" s="7">
+    <row r="18" ht="79" customHeight="1" s="10">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -3244,7 +3303,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="79" customHeight="1" s="7">
+    <row r="19" ht="79" customHeight="1" s="10">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>1.8b</t>
@@ -3267,7 +3326,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="79" customHeight="1" s="7">
+    <row r="20" ht="79" customHeight="1" s="10">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>1.8c</t>
@@ -3290,7 +3349,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1" s="7">
+    <row r="21" ht="19" customHeight="1" s="10">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -3309,14 +3368,14 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="5" t="n"/>
     </row>
-    <row r="22" ht="34" customHeight="1" s="7">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22" ht="34" customHeight="1" s="10">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>2 · Abriter les sinistrés</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1" s="7">
+    <row r="23" ht="19" customHeight="1" s="10">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -3335,7 +3394,7 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="5" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="7">
+    <row r="24" ht="19" customHeight="1" s="10">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
@@ -3362,7 +3421,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="34" customHeight="1" s="7">
+    <row r="25" ht="34" customHeight="1" s="10">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -3385,7 +3444,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1" s="7">
+    <row r="26" ht="19" customHeight="1" s="10">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
@@ -3404,7 +3463,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="5" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="7">
+    <row r="27" ht="19" customHeight="1" s="10">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3427,7 +3486,7 @@
       </c>
       <c r="E27" s="5" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="7">
+    <row r="28" ht="19" customHeight="1" s="10">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -3446,7 +3505,7 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="5" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="7">
+    <row r="29" ht="19" customHeight="1" s="10">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -3465,7 +3524,7 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="5" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="7">
+    <row r="30" ht="19" customHeight="1" s="10">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -3484,7 +3543,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="5" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="7">
+    <row r="31" ht="19" customHeight="1" s="10">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -3507,7 +3566,7 @@
       </c>
       <c r="E31" s="5" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="7">
+    <row r="32" ht="19" customHeight="1" s="10">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2.10</t>
@@ -3526,7 +3585,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="5" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="7">
+    <row r="33" ht="19" customHeight="1" s="10">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -3545,7 +3604,7 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="5" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="7">
+    <row r="34" ht="19" customHeight="1" s="10">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2.12</t>
@@ -3568,7 +3627,7 @@
       </c>
       <c r="E34" s="5" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="7">
+    <row r="35" ht="19" customHeight="1" s="10">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2.13</t>
@@ -3591,7 +3650,7 @@
       </c>
       <c r="E35" s="5" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1" s="7">
+    <row r="36" ht="34" customHeight="1" s="10">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2.14</t>
@@ -3618,7 +3677,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1" s="7">
+    <row r="37" ht="34" customHeight="1" s="10">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -3637,7 +3696,7 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="5" t="n"/>
     </row>
-    <row r="38" ht="34" customHeight="1" s="7">
+    <row r="38" ht="34" customHeight="1" s="10">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2.16</t>
@@ -3656,7 +3715,7 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="5" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="7">
+    <row r="39" ht="19" customHeight="1" s="10">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2.17</t>
@@ -3679,7 +3738,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="19" customHeight="1" s="7">
+    <row r="40" ht="19" customHeight="1" s="10">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>2.18</t>
@@ -3698,7 +3757,7 @@
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="5" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="7">
+    <row r="41" ht="19" customHeight="1" s="10">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>2.19</t>
@@ -3717,7 +3776,7 @@
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="5" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="7">
+    <row r="42" ht="19" customHeight="1" s="10">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2.20</t>
@@ -3736,7 +3795,7 @@
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="5" t="n"/>
     </row>
-    <row r="43" ht="49" customHeight="1" s="7">
+    <row r="43" ht="49" customHeight="1" s="10">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2.21</t>
@@ -3755,7 +3814,7 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="5" t="n"/>
     </row>
-    <row r="44" ht="34" customHeight="1" s="7">
+    <row r="44" ht="34" customHeight="1" s="10">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2.22</t>
@@ -3774,7 +3833,7 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="5" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="7">
+    <row r="45" ht="19" customHeight="1" s="10">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2.23</t>
@@ -3798,7 +3857,7 @@
       </c>
       <c r="E45" s="5" t="n"/>
     </row>
-    <row r="46" ht="19" customHeight="1" s="7">
+    <row r="46" ht="19" customHeight="1" s="10">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -3817,7 +3876,7 @@
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="5" t="n"/>
     </row>
-    <row r="47" ht="34" customHeight="1" s="7">
+    <row r="47" ht="34" customHeight="1" s="10">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -3836,7 +3895,7 @@
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="5" t="n"/>
     </row>
-    <row r="48" ht="19" customHeight="1" s="7">
+    <row r="48" ht="19" customHeight="1" s="10">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>2.26</t>
@@ -3855,7 +3914,7 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="5" t="n"/>
     </row>
-    <row r="49" ht="19" customHeight="1" s="7">
+    <row r="49" ht="19" customHeight="1" s="10">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>2.27</t>
@@ -3874,7 +3933,7 @@
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="5" t="n"/>
     </row>
-    <row r="50" ht="19" customHeight="1" s="7">
+    <row r="50" ht="19" customHeight="1" s="10">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -3893,7 +3952,7 @@
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="5" t="n"/>
     </row>
-    <row r="51" ht="19" customHeight="1" s="7">
+    <row r="51" ht="19" customHeight="1" s="10">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>2.29</t>
@@ -3912,7 +3971,7 @@
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="5" t="n"/>
     </row>
-    <row r="52" ht="22" customHeight="1" s="7">
+    <row r="52" ht="22" customHeight="1" s="10">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>2.30</t>
@@ -3931,7 +3990,7 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="5" t="n"/>
     </row>
-    <row r="53" ht="19" customHeight="1" s="7">
+    <row r="53" ht="19" customHeight="1" s="10">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>2.31</t>
@@ -3950,14 +4009,14 @@
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="5" t="n"/>
     </row>
-    <row r="54" ht="34" customHeight="1" s="7">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="54" ht="34" customHeight="1" s="10">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>3 · Choisir un pont</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="19" customHeight="1" s="7">
+    <row r="55" ht="19" customHeight="1" s="10">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -3976,7 +4035,7 @@
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="5" t="n"/>
     </row>
-    <row r="56" ht="19" customHeight="1" s="7">
+    <row r="56" ht="19" customHeight="1" s="10">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -3999,7 +4058,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="19" customHeight="1" s="7">
+    <row r="57" ht="19" customHeight="1" s="10">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -4018,7 +4077,7 @@
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="5" t="n"/>
     </row>
-    <row r="58" ht="19" customHeight="1" s="7">
+    <row r="58" ht="19" customHeight="1" s="10">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -4037,7 +4096,7 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="5" t="n"/>
     </row>
-    <row r="59" ht="19" customHeight="1" s="7">
+    <row r="59" ht="19" customHeight="1" s="10">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -4056,7 +4115,7 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="5" t="n"/>
     </row>
-    <row r="60" ht="19" customHeight="1" s="7">
+    <row r="60" ht="19" customHeight="1" s="10">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
@@ -4075,7 +4134,7 @@
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="5" t="n"/>
     </row>
-    <row r="61" ht="19" customHeight="1" s="7">
+    <row r="61" ht="19" customHeight="1" s="10">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -4094,7 +4153,7 @@
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="5" t="n"/>
     </row>
-    <row r="62" ht="19" customHeight="1" s="7">
+    <row r="62" ht="19" customHeight="1" s="10">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -4113,7 +4172,7 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="5" t="n"/>
     </row>
-    <row r="63" ht="19" customHeight="1" s="7">
+    <row r="63" ht="19" customHeight="1" s="10">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>3.9</t>
@@ -4132,7 +4191,7 @@
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="5" t="n"/>
     </row>
-    <row r="64" ht="19" customHeight="1" s="7">
+    <row r="64" ht="19" customHeight="1" s="10">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>3.10</t>
@@ -4155,7 +4214,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="19" customHeight="1" s="7">
+    <row r="65" ht="19" customHeight="1" s="10">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>3.11</t>
@@ -4174,7 +4233,7 @@
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="5" t="n"/>
     </row>
-    <row r="66" ht="34" customHeight="1" s="7">
+    <row r="66" ht="34" customHeight="1" s="10">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>3.12</t>
@@ -4193,7 +4252,7 @@
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="5" t="n"/>
     </row>
-    <row r="67" ht="34" customHeight="1" s="7">
+    <row r="67" ht="34" customHeight="1" s="10">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>3.13</t>
@@ -4216,7 +4275,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="19" customHeight="1" s="7">
+    <row r="68" ht="19" customHeight="1" s="10">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>3.14</t>
@@ -4235,7 +4294,7 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="5" t="n"/>
     </row>
-    <row r="69" ht="19" customHeight="1" s="7">
+    <row r="69" ht="19" customHeight="1" s="10">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>3.15</t>
@@ -4254,7 +4313,7 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="5" t="n"/>
     </row>
-    <row r="70" ht="19" customHeight="1" s="7">
+    <row r="70" ht="19" customHeight="1" s="10">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>3.16</t>
@@ -4273,7 +4332,7 @@
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="5" t="n"/>
     </row>
-    <row r="71" ht="19" customHeight="1" s="7">
+    <row r="71" ht="19" customHeight="1" s="10">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4292,7 +4351,7 @@
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="5" t="n"/>
     </row>
-    <row r="72" ht="19" customHeight="1" s="7">
+    <row r="72" ht="19" customHeight="1" s="10">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>3.18</t>
@@ -4311,7 +4370,7 @@
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="5" t="n"/>
     </row>
-    <row r="73" ht="22" customHeight="1" s="7">
+    <row r="73" ht="22" customHeight="1" s="10">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -4330,7 +4389,7 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="5" t="n"/>
     </row>
-    <row r="74" ht="34" customHeight="1" s="7">
+    <row r="74" ht="34" customHeight="1" s="10">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>3.20</t>
@@ -4349,14 +4408,14 @@
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="5" t="n"/>
     </row>
-    <row r="75" ht="19" customHeight="1" s="7">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="75" ht="19" customHeight="1" s="10">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>4 · La boue sur le chemin du pont</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="19" customHeight="1" s="7">
+    <row r="76" ht="19" customHeight="1" s="10">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -4379,7 +4438,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="19" customHeight="1" s="7">
+    <row r="77" ht="19" customHeight="1" s="10">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -4398,7 +4457,7 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="5" t="n"/>
     </row>
-    <row r="78" ht="19" customHeight="1" s="7">
+    <row r="78" ht="19" customHeight="1" s="10">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -4417,7 +4476,7 @@
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="5" t="n"/>
     </row>
-    <row r="79" ht="19" customHeight="1" s="7">
+    <row r="79" ht="19" customHeight="1" s="10">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -4436,7 +4495,7 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="5" t="n"/>
     </row>
-    <row r="80" ht="19" customHeight="1" s="7">
+    <row r="80" ht="19" customHeight="1" s="10">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -4455,7 +4514,7 @@
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="5" t="n"/>
     </row>
-    <row r="81" ht="34" customHeight="1" s="7">
+    <row r="81" ht="34" customHeight="1" s="10">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -4474,7 +4533,7 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="5" t="n"/>
     </row>
-    <row r="82" ht="34" customHeight="1" s="7">
+    <row r="82" ht="34" customHeight="1" s="10">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -4493,7 +4552,7 @@
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="5" t="n"/>
     </row>
-    <row r="83" ht="19" customHeight="1" s="7">
+    <row r="83" ht="19" customHeight="1" s="10">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -4512,7 +4571,7 @@
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="5" t="n"/>
     </row>
-    <row r="84" ht="19" customHeight="1" s="7">
+    <row r="84" ht="19" customHeight="1" s="10">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -4531,7 +4590,7 @@
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="5" t="n"/>
     </row>
-    <row r="85" ht="19" customHeight="1" s="7">
+    <row r="85" ht="19" customHeight="1" s="10">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>4.10</t>
@@ -4550,7 +4609,7 @@
       <c r="D85" s="4" t="n"/>
       <c r="E85" s="5" t="n"/>
     </row>
-    <row r="86" ht="19" customHeight="1" s="7">
+    <row r="86" ht="19" customHeight="1" s="10">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>4.11</t>
@@ -4569,7 +4628,7 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="5" t="n"/>
     </row>
-    <row r="87" ht="19" customHeight="1" s="7">
+    <row r="87" ht="19" customHeight="1" s="10">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>4.12</t>
@@ -4588,7 +4647,7 @@
       <c r="D87" s="4" t="n"/>
       <c r="E87" s="5" t="n"/>
     </row>
-    <row r="88" ht="19" customHeight="1" s="7">
+    <row r="88" ht="19" customHeight="1" s="10">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>4.13</t>
@@ -4607,7 +4666,7 @@
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="5" t="n"/>
     </row>
-    <row r="89" ht="34" customHeight="1" s="7">
+    <row r="89" ht="34" customHeight="1" s="10">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>4.14</t>
@@ -4626,7 +4685,7 @@
       <c r="D89" s="4" t="n"/>
       <c r="E89" s="5" t="n"/>
     </row>
-    <row r="90" ht="22" customHeight="1" s="7">
+    <row r="90" ht="22" customHeight="1" s="10">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>4.15</t>
@@ -4645,7 +4704,7 @@
       <c r="D90" s="4" t="n"/>
       <c r="E90" s="5" t="n"/>
     </row>
-    <row r="91" ht="19" customHeight="1" s="7">
+    <row r="91" ht="19" customHeight="1" s="10">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>4.16</t>
@@ -4664,14 +4723,14 @@
       <c r="D91" s="4" t="n"/>
       <c r="E91" s="5" t="n"/>
     </row>
-    <row r="92" ht="49" customHeight="1" s="7">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="92" ht="49" customHeight="1" s="10">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>5 · Le pont rouvert, l'étude de l'université</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="19" customHeight="1" s="7">
+    <row r="93" ht="19" customHeight="1" s="10">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -4694,7 +4753,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="34" customHeight="1" s="7">
+    <row r="94" ht="34" customHeight="1" s="10">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -4714,7 +4773,7 @@
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="5" t="n"/>
     </row>
-    <row r="95" ht="19" customHeight="1" s="7">
+    <row r="95" ht="19" customHeight="1" s="10">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -4733,7 +4792,7 @@
       <c r="D95" s="4" t="n"/>
       <c r="E95" s="5" t="n"/>
     </row>
-    <row r="96" ht="19" customHeight="1" s="7">
+    <row r="96" ht="19" customHeight="1" s="10">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -4752,7 +4811,7 @@
       <c r="D96" s="4" t="n"/>
       <c r="E96" s="5" t="n"/>
     </row>
-    <row r="97" ht="19" customHeight="1" s="7">
+    <row r="97" ht="19" customHeight="1" s="10">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -4771,7 +4830,7 @@
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="5" t="n"/>
     </row>
-    <row r="98" ht="19" customHeight="1" s="7">
+    <row r="98" ht="19" customHeight="1" s="10">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -4790,7 +4849,7 @@
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="5" t="n"/>
     </row>
-    <row r="99" ht="34" customHeight="1" s="7">
+    <row r="99" ht="34" customHeight="1" s="10">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -4809,7 +4868,7 @@
       <c r="D99" s="4" t="n"/>
       <c r="E99" s="5" t="n"/>
     </row>
-    <row r="100" ht="19" customHeight="1" s="7">
+    <row r="100" ht="19" customHeight="1" s="10">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -4828,7 +4887,7 @@
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="5" t="n"/>
     </row>
-    <row r="101" ht="19" customHeight="1" s="7">
+    <row r="101" ht="19" customHeight="1" s="10">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -4847,7 +4906,7 @@
       <c r="D101" s="4" t="n"/>
       <c r="E101" s="5" t="n"/>
     </row>
-    <row r="102" ht="109" customHeight="1" s="7">
+    <row r="102" ht="109" customHeight="1" s="10">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>5.10</t>
@@ -4866,7 +4925,7 @@
       <c r="D102" s="4" t="n"/>
       <c r="E102" s="5" t="n"/>
     </row>
-    <row r="103" ht="19" customHeight="1" s="7">
+    <row r="103" ht="19" customHeight="1" s="10">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>5.11</t>
@@ -4885,7 +4944,7 @@
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="5" t="n"/>
     </row>
-    <row r="104" ht="19" customHeight="1" s="7">
+    <row r="104" ht="19" customHeight="1" s="10">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>5.12</t>
@@ -4905,7 +4964,7 @@
       <c r="D104" s="4" t="n"/>
       <c r="E104" s="5" t="n"/>
     </row>
-    <row r="105" ht="19" customHeight="1" s="7">
+    <row r="105" ht="19" customHeight="1" s="10">
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>5.13</t>
@@ -4924,7 +4983,7 @@
       <c r="D105" s="4" t="n"/>
       <c r="E105" s="5" t="n"/>
     </row>
-    <row r="106" ht="34" customHeight="1" s="7">
+    <row r="106" ht="34" customHeight="1" s="10">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>5.14</t>
@@ -4943,7 +5002,7 @@
       <c r="D106" s="4" t="n"/>
       <c r="E106" s="5" t="n"/>
     </row>
-    <row r="107" ht="19" customHeight="1" s="7">
+    <row r="107" ht="19" customHeight="1" s="10">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>5.15</t>
@@ -4966,7 +5025,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="64" customHeight="1" s="7">
+    <row r="108" ht="64" customHeight="1" s="10">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>5.16</t>
@@ -4985,7 +5044,7 @@
       <c r="D108" s="4" t="n"/>
       <c r="E108" s="5" t="n"/>
     </row>
-    <row r="109" ht="64" customHeight="1" s="7">
+    <row r="109" ht="64" customHeight="1" s="10">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -5004,7 +5063,7 @@
       <c r="D109" s="4" t="n"/>
       <c r="E109" s="5" t="n"/>
     </row>
-    <row r="110" ht="49" customHeight="1" s="7">
+    <row r="110" ht="49" customHeight="1" s="10">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>5.18</t>
@@ -5024,7 +5083,7 @@
       <c r="D110" s="4" t="n"/>
       <c r="E110" s="5" t="n"/>
     </row>
-    <row r="111" ht="49" customHeight="1" s="7">
+    <row r="111" ht="49" customHeight="1" s="10">
       <c r="A111" s="2" t="inlineStr">
         <is>
           <t>5.19</t>
@@ -5044,7 +5103,7 @@
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="5" t="n"/>
     </row>
-    <row r="112" ht="19" customHeight="1" s="7">
+    <row r="112" ht="19" customHeight="1" s="10">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>5.20</t>
@@ -5065,7 +5124,7 @@
       <c r="D112" s="4" t="n"/>
       <c r="E112" s="5" t="n"/>
     </row>
-    <row r="113" ht="49" customHeight="1" s="7">
+    <row r="113" ht="49" customHeight="1" s="10">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>5.21</t>
@@ -5084,7 +5143,7 @@
       <c r="D113" s="4" t="n"/>
       <c r="E113" s="5" t="n"/>
     </row>
-    <row r="114" ht="49" customHeight="1" s="7">
+    <row r="114" ht="49" customHeight="1" s="10">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>5.22</t>
@@ -5103,7 +5162,7 @@
       <c r="D114" s="4" t="n"/>
       <c r="E114" s="5" t="n"/>
     </row>
-    <row r="115" ht="49" customHeight="1" s="7">
+    <row r="115" ht="49" customHeight="1" s="10">
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>5.23</t>
@@ -5124,7 +5183,7 @@
       <c r="D115" s="4" t="n"/>
       <c r="E115" s="5" t="n"/>
     </row>
-    <row r="116" ht="49" customHeight="1" s="7">
+    <row r="116" ht="49" customHeight="1" s="10">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>5.24</t>
@@ -5145,7 +5204,7 @@
       <c r="D116" s="4" t="n"/>
       <c r="E116" s="5" t="n"/>
     </row>
-    <row r="117" ht="22" customHeight="1" s="7">
+    <row r="117" ht="22" customHeight="1" s="10">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>5.25</t>
@@ -5166,7 +5225,7 @@
       <c r="D117" s="4" t="n"/>
       <c r="E117" s="5" t="n"/>
     </row>
-    <row r="118" ht="19" customHeight="1" s="7">
+    <row r="118" ht="19" customHeight="1" s="10">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>5.26</t>
@@ -5187,14 +5246,14 @@
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="5" t="n"/>
     </row>
-    <row r="119" ht="34" customHeight="1" s="7">
-      <c r="A119" s="6" t="inlineStr">
+    <row r="119" ht="34" customHeight="1" s="10">
+      <c r="A119" s="12" t="inlineStr">
         <is>
           <t>6 · La bibliothèque (s'ouvre avec l'étude)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="19" customHeight="1" s="7">
+    <row r="120" ht="19" customHeight="1" s="10">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>6.1</t>
@@ -5213,7 +5272,7 @@
       <c r="D120" s="4" t="n"/>
       <c r="E120" s="5" t="n"/>
     </row>
-    <row r="121" ht="79" customHeight="1" s="7">
+    <row r="121" ht="79" customHeight="1" s="10">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
@@ -5232,7 +5291,7 @@
       <c r="D121" s="4" t="n"/>
       <c r="E121" s="5" t="n"/>
     </row>
-    <row r="122" ht="19" customHeight="1" s="7">
+    <row r="122" ht="19" customHeight="1" s="10">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>6.3</t>
@@ -5251,7 +5310,7 @@
       <c r="D122" s="4" t="n"/>
       <c r="E122" s="5" t="n"/>
     </row>
-    <row r="123" ht="64" customHeight="1" s="7">
+    <row r="123" ht="64" customHeight="1" s="10">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -5270,7 +5329,7 @@
       <c r="D123" s="4" t="n"/>
       <c r="E123" s="5" t="n"/>
     </row>
-    <row r="124" ht="19" customHeight="1" s="7">
+    <row r="124" ht="19" customHeight="1" s="10">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -5289,7 +5348,7 @@
       <c r="D124" s="4" t="n"/>
       <c r="E124" s="5" t="n"/>
     </row>
-    <row r="125" ht="64" customHeight="1" s="7">
+    <row r="125" ht="64" customHeight="1" s="10">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>6.6</t>
@@ -5308,7 +5367,7 @@
       <c r="D125" s="4" t="n"/>
       <c r="E125" s="5" t="n"/>
     </row>
-    <row r="126" ht="64" customHeight="1" s="7">
+    <row r="126" ht="64" customHeight="1" s="10">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>6.7</t>
@@ -5327,7 +5386,7 @@
       <c r="D126" s="4" t="n"/>
       <c r="E126" s="5" t="n"/>
     </row>
-    <row r="127" ht="19" customHeight="1" s="7">
+    <row r="127" ht="19" customHeight="1" s="10">
       <c r="A127" s="2" t="inlineStr">
         <is>
           <t>6.8</t>
@@ -5346,7 +5405,7 @@
       <c r="D127" s="4" t="n"/>
       <c r="E127" s="5" t="n"/>
     </row>
-    <row r="128" ht="19" customHeight="1" s="7">
+    <row r="128" ht="19" customHeight="1" s="10">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>6.9</t>
@@ -5368,7 +5427,7 @@
       <c r="D128" s="4" t="n"/>
       <c r="E128" s="5" t="n"/>
     </row>
-    <row r="129" ht="34" customHeight="1" s="7">
+    <row r="129" ht="34" customHeight="1" s="10">
       <c r="A129" s="2" t="inlineStr">
         <is>
           <t>6.10</t>
@@ -5387,7 +5446,7 @@
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="5" t="n"/>
     </row>
-    <row r="130" ht="19" customHeight="1" s="7">
+    <row r="130" ht="19" customHeight="1" s="10">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>6.11</t>
@@ -5406,7 +5465,7 @@
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="5" t="n"/>
     </row>
-    <row r="131" ht="22" customHeight="1" s="7">
+    <row r="131" ht="22" customHeight="1" s="10">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>6.12</t>
@@ -5425,7 +5484,7 @@
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="5" t="n"/>
     </row>
-    <row r="132" ht="19" customHeight="1" s="7">
+    <row r="132" ht="19" customHeight="1" s="10">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>6.13</t>
@@ -5444,14 +5503,14 @@
       <c r="D132" s="4" t="n"/>
       <c r="E132" s="5" t="n"/>
     </row>
-    <row r="133" ht="49" customHeight="1" s="7">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="133" ht="49" customHeight="1" s="10">
+      <c r="A133" s="12" t="inlineStr">
         <is>
           <t>7 · Le camp se plaint (un mois après le lancement du pont)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="19" customHeight="1" s="7">
+    <row r="134" ht="19" customHeight="1" s="10">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>7.1</t>
@@ -5474,7 +5533,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="34" customHeight="1" s="7">
+    <row r="135" ht="34" customHeight="1" s="10">
       <c r="A135" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
@@ -5494,7 +5553,7 @@
       <c r="D135" s="4" t="n"/>
       <c r="E135" s="5" t="n"/>
     </row>
-    <row r="136" ht="19" customHeight="1" s="7">
+    <row r="136" ht="19" customHeight="1" s="10">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -5513,7 +5572,7 @@
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="5" t="n"/>
     </row>
-    <row r="137" ht="34" customHeight="1" s="7">
+    <row r="137" ht="34" customHeight="1" s="10">
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -5532,7 +5591,7 @@
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="5" t="n"/>
     </row>
-    <row r="138" ht="19" customHeight="1" s="7">
+    <row r="138" ht="19" customHeight="1" s="10">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -5551,7 +5610,7 @@
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="5" t="n"/>
     </row>
-    <row r="139" ht="64" customHeight="1" s="7">
+    <row r="139" ht="64" customHeight="1" s="10">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>7.6</t>
@@ -5570,7 +5629,7 @@
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="5" t="n"/>
     </row>
-    <row r="140" ht="79" customHeight="1" s="7">
+    <row r="140" ht="79" customHeight="1" s="10">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>7.7</t>
@@ -5589,7 +5648,7 @@
       <c r="D140" s="4" t="n"/>
       <c r="E140" s="5" t="n"/>
     </row>
-    <row r="141" ht="22" customHeight="1" s="7">
+    <row r="141" ht="22" customHeight="1" s="10">
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>7.8</t>
@@ -5610,7 +5669,7 @@
       <c r="D141" s="4" t="n"/>
       <c r="E141" s="5" t="n"/>
     </row>
-    <row r="142" ht="19" customHeight="1" s="7">
+    <row r="142" ht="19" customHeight="1" s="10">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>7.9</t>
@@ -5630,14 +5689,14 @@
       <c r="D142" s="4" t="n"/>
       <c r="E142" s="5" t="n"/>
     </row>
-    <row r="143" ht="49" customHeight="1" s="7">
-      <c r="A143" s="6" t="inlineStr">
+    <row r="143" ht="49" customHeight="1" s="10">
+      <c r="A143" s="12" t="inlineStr">
         <is>
           <t>8 · Après l'étude : le premier lieu à relever</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="34" customHeight="1" s="7">
+    <row r="144" ht="34" customHeight="1" s="10">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>8.1</t>
@@ -5656,7 +5715,7 @@
       <c r="D144" s="4" t="n"/>
       <c r="E144" s="5" t="n"/>
     </row>
-    <row r="145" ht="94" customHeight="1" s="7">
+    <row r="145" ht="94" customHeight="1" s="10">
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>8.2</t>
@@ -5676,7 +5735,7 @@
       <c r="D145" s="4" t="n"/>
       <c r="E145" s="5" t="n"/>
     </row>
-    <row r="146" ht="19" customHeight="1" s="7">
+    <row r="146" ht="19" customHeight="1" s="10">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -5695,7 +5754,7 @@
       <c r="D146" s="4" t="n"/>
       <c r="E146" s="5" t="n"/>
     </row>
-    <row r="147" ht="34" customHeight="1" s="7">
+    <row r="147" ht="34" customHeight="1" s="10">
       <c r="A147" s="2" t="inlineStr">
         <is>
           <t>8.4</t>
@@ -5718,7 +5777,7 @@
       <c r="D147" s="4" t="n"/>
       <c r="E147" s="5" t="n"/>
     </row>
-    <row r="148" ht="34" customHeight="1" s="7">
+    <row r="148" ht="34" customHeight="1" s="10">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>8.5</t>
@@ -5737,7 +5796,7 @@
       <c r="D148" s="4" t="n"/>
       <c r="E148" s="5" t="n"/>
     </row>
-    <row r="149" ht="19" customHeight="1" s="7">
+    <row r="149" ht="19" customHeight="1" s="10">
       <c r="A149" s="2" t="inlineStr">
         <is>
           <t>8.6</t>
@@ -5757,7 +5816,7 @@
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="5" t="n"/>
     </row>
-    <row r="150" ht="34" customHeight="1" s="7">
+    <row r="150" ht="34" customHeight="1" s="10">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>8.7</t>
@@ -5776,7 +5835,7 @@
       <c r="D150" s="4" t="n"/>
       <c r="E150" s="5" t="n"/>
     </row>
-    <row r="151" ht="34" customHeight="1" s="7">
+    <row r="151" ht="34" customHeight="1" s="10">
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>8.8</t>
@@ -5799,7 +5858,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="34" customHeight="1" s="7">
+    <row r="152" ht="34" customHeight="1" s="10">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>8.9</t>
@@ -5818,7 +5877,7 @@
       <c r="D152" s="4" t="n"/>
       <c r="E152" s="5" t="n"/>
     </row>
-    <row r="153" ht="34" customHeight="1" s="7">
+    <row r="153" ht="34" customHeight="1" s="10">
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>8.10</t>
@@ -5837,7 +5896,7 @@
       <c r="D153" s="4" t="n"/>
       <c r="E153" s="5" t="n"/>
     </row>
-    <row r="154" ht="34" customHeight="1" s="7">
+    <row r="154" ht="34" customHeight="1" s="10">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>8.11</t>
@@ -5856,7 +5915,7 @@
       <c r="D154" s="4" t="n"/>
       <c r="E154" s="5" t="n"/>
     </row>
-    <row r="155" ht="19" customHeight="1" s="7">
+    <row r="155" ht="19" customHeight="1" s="10">
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>8.12</t>
@@ -5875,7 +5934,7 @@
       <c r="D155" s="4" t="n"/>
       <c r="E155" s="5" t="n"/>
     </row>
-    <row r="156" ht="19" customHeight="1" s="7">
+    <row r="156" ht="19" customHeight="1" s="10">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>8.13</t>
@@ -5894,7 +5953,7 @@
       <c r="D156" s="4" t="n"/>
       <c r="E156" s="5" t="n"/>
     </row>
-    <row r="157" ht="34" customHeight="1" s="7">
+    <row r="157" ht="34" customHeight="1" s="10">
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>8.14</t>
@@ -5913,7 +5972,7 @@
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="5" t="n"/>
     </row>
-    <row r="158" ht="64" customHeight="1" s="7">
+    <row r="158" ht="64" customHeight="1" s="10">
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>8.15</t>
@@ -5932,7 +5991,7 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="5" t="n"/>
     </row>
-    <row r="159" ht="34" customHeight="1" s="7">
+    <row r="159" ht="34" customHeight="1" s="10">
       <c r="A159" s="2" t="inlineStr">
         <is>
           <t>8.16</t>
@@ -5952,7 +6011,7 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="5" t="n"/>
     </row>
-    <row r="160" ht="49" customHeight="1" s="7">
+    <row r="160" ht="49" customHeight="1" s="10">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>8.17</t>
@@ -5971,7 +6030,7 @@
       <c r="D160" s="4" t="n"/>
       <c r="E160" s="5" t="n"/>
     </row>
-    <row r="161" ht="19" customHeight="1" s="7">
+    <row r="161" ht="19" customHeight="1" s="10">
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>8.18</t>
@@ -5991,7 +6050,7 @@
       <c r="D161" s="4" t="n"/>
       <c r="E161" s="5" t="n"/>
     </row>
-    <row r="162" ht="19" customHeight="1" s="7">
+    <row r="162" ht="19" customHeight="1" s="10">
       <c r="A162" s="2" t="inlineStr">
         <is>
           <t>8.19</t>
@@ -6012,7 +6071,7 @@
       <c r="D162" s="4" t="n"/>
       <c r="E162" s="5" t="n"/>
     </row>
-    <row r="163" ht="22" customHeight="1" s="7">
+    <row r="163" ht="22" customHeight="1" s="10">
       <c r="A163" s="2" t="inlineStr">
         <is>
           <t>8.20</t>
@@ -6031,7 +6090,7 @@
       <c r="D163" s="4" t="n"/>
       <c r="E163" s="5" t="n"/>
     </row>
-    <row r="164" ht="19" customHeight="1" s="7">
+    <row r="164" ht="19" customHeight="1" s="10">
       <c r="A164" s="2" t="inlineStr">
         <is>
           <t>8.21</t>
@@ -6050,14 +6109,14 @@
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="5" t="n"/>
     </row>
-    <row r="165" ht="19" customHeight="1" s="7">
-      <c r="A165" s="6" t="inlineStr">
+    <row r="165" ht="19" customHeight="1" s="10">
+      <c r="A165" s="12" t="inlineStr">
         <is>
           <t>9 · Les noms vus pendant ces minutes</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="19" customHeight="1" s="7">
+    <row r="166" ht="19" customHeight="1" s="10">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>9.1</t>
@@ -6080,7 +6139,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="19" customHeight="1" s="7">
+    <row r="167" ht="19" customHeight="1" s="10">
       <c r="A167" s="2" t="inlineStr">
         <is>
           <t>9.2</t>
@@ -6103,7 +6162,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="19" customHeight="1" s="7">
+    <row r="168" ht="19" customHeight="1" s="10">
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>9.3</t>
@@ -6126,7 +6185,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="19" customHeight="1" s="7">
+    <row r="169" ht="19" customHeight="1" s="10">
       <c r="A169" s="2" t="inlineStr">
         <is>
           <t>9.4</t>
@@ -6145,7 +6204,7 @@
       <c r="D169" s="4" t="n"/>
       <c r="E169" s="5" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" s="10">
       <c r="A170" s="2" t="inlineStr">
         <is>
           <t>9.5</t>
@@ -6168,7 +6227,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" s="10">
       <c r="A171" s="2" t="inlineStr">
         <is>
           <t>9.6</t>
@@ -6187,19 +6246,20 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="5" t="n"/>
     </row>
+    <row r="172" s="10"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A165:E165"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A92:E92"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A143:E143"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
